--- a/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Ritiro rifiuti ingombranti.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Ritiro rifiuti ingombranti.xlsx
@@ -929,7 +929,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -990,7 +990,7 @@
     <t>Disdici appuntamento</t>
   </si>
   <si>
-    <t>Vedi avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>-</t>
@@ -1089,7 +1089,7 @@
     <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
   </si>
   <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
+    <t xml:space="preserve">**Promemoria automatici — **Messaggi Premium
 Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
 Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
